--- a/Assets/GameData/Excel/Enemy.xlsx
+++ b/Assets/GameData/Excel/Enemy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\NewUnityHub\UnityDevTool\UnityTool_ExcelToData\UnityTool_ExcelToData\Assets\GameData\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBB535BC-3F18-42DD-B16D-45AA1057B8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E190F361-6F3F-4287-8D30-2C7710F9218E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="23040" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enemy" sheetId="1" r:id="rId1"/>
@@ -565,7 +565,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2001</v>
+        <v>1003</v>
       </c>
       <c r="B6" t="s">
         <v>18</v>
